--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="603">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1745,6 +1745,84 @@
   </si>
   <si>
     <t>NSE:SONACOMS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772012700_1772096400</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:54</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771993800_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:00</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:15</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BULL_1771992000_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BULL_1771996500_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:45</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ_BEAR_1771993800_1772092800</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:30</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1772078400_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:15</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:55</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ_BEAR_1772092800_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772098200</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:00</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ_BULL_1771994700_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772098200</t>
   </si>
 </sst>
 </file>
@@ -2208,7 +2286,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N158"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -7577,6 +7655,402 @@
         <v>574</v>
       </c>
     </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="E159" s="12">
+        <v>439.5</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="G159" s="12">
+        <v>447.35</v>
+      </c>
+      <c r="H159" s="12">
+        <v>445.4</v>
+      </c>
+      <c r="I159" s="12">
+        <v>447.3</v>
+      </c>
+      <c r="J159" s="11"/>
+      <c r="K159" s="11"/>
+      <c r="L159" s="11"/>
+      <c r="M159" s="11"/>
+      <c r="N159" s="11" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="E160" s="12">
+        <v>924.3</v>
+      </c>
+      <c r="F160" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="G160" s="12">
+        <v>948</v>
+      </c>
+      <c r="H160" s="12">
+        <v>935.15</v>
+      </c>
+      <c r="I160" s="12">
+        <v>947.55</v>
+      </c>
+      <c r="J160" s="11"/>
+      <c r="K160" s="11"/>
+      <c r="L160" s="11"/>
+      <c r="M160" s="11"/>
+      <c r="N160" s="11" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161" s="11" t="s">
+        <v>583</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E161" s="12">
+        <v>169.44</v>
+      </c>
+      <c r="F161" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="G161" s="12">
+        <v>171.2</v>
+      </c>
+      <c r="H161" s="12">
+        <v>170.3</v>
+      </c>
+      <c r="I161" s="12">
+        <v>170.66</v>
+      </c>
+      <c r="J161" s="11"/>
+      <c r="K161" s="11"/>
+      <c r="L161" s="11"/>
+      <c r="M161" s="11"/>
+      <c r="N161" s="11" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A162" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C162" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="E162" s="12">
+        <v>126.57</v>
+      </c>
+      <c r="F162" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="G162" s="12">
+        <v>130.7</v>
+      </c>
+      <c r="H162" s="12">
+        <v>128.61</v>
+      </c>
+      <c r="I162" s="12">
+        <v>129.65</v>
+      </c>
+      <c r="J162" s="11"/>
+      <c r="K162" s="11"/>
+      <c r="L162" s="11"/>
+      <c r="M162" s="11"/>
+      <c r="N162" s="11" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A163" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C163" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="E163" s="12">
+        <v>3927.4</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="G163" s="12">
+        <v>3987.9</v>
+      </c>
+      <c r="H163" s="12">
+        <v>3916</v>
+      </c>
+      <c r="I163" s="12">
+        <v>3966.1</v>
+      </c>
+      <c r="J163" s="11"/>
+      <c r="K163" s="11"/>
+      <c r="L163" s="11"/>
+      <c r="M163" s="11"/>
+      <c r="N163" s="11" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="C164" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="E164" s="10">
+        <v>427.5</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="G164" s="10">
+        <v>424.6</v>
+      </c>
+      <c r="H164" s="10">
+        <v>423</v>
+      </c>
+      <c r="I164" s="10">
+        <v>423.15</v>
+      </c>
+      <c r="J164" s="9"/>
+      <c r="K164" s="9"/>
+      <c r="L164" s="9"/>
+      <c r="M164" s="9"/>
+      <c r="N164" s="9" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="E165" s="12">
+        <v>6760</v>
+      </c>
+      <c r="F165" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="G165" s="12">
+        <v>6880</v>
+      </c>
+      <c r="H165" s="12">
+        <v>6840.5</v>
+      </c>
+      <c r="I165" s="12">
+        <v>6870</v>
+      </c>
+      <c r="J165" s="11"/>
+      <c r="K165" s="11"/>
+      <c r="L165" s="11"/>
+      <c r="M165" s="11"/>
+      <c r="N165" s="11" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="C166" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="E166" s="10">
+        <v>130</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="G166" s="10">
+        <v>130.72</v>
+      </c>
+      <c r="H166" s="10">
+        <v>130.13</v>
+      </c>
+      <c r="I166" s="10">
+        <v>130.14</v>
+      </c>
+      <c r="J166" s="9"/>
+      <c r="K166" s="9"/>
+      <c r="L166" s="9"/>
+      <c r="M166" s="9"/>
+      <c r="N166" s="9" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A167" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="C167" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="E167" s="12">
+        <v>538</v>
+      </c>
+      <c r="F167" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="G167" s="12">
+        <v>546</v>
+      </c>
+      <c r="H167" s="12">
+        <v>543.15</v>
+      </c>
+      <c r="I167" s="12">
+        <v>545.3</v>
+      </c>
+      <c r="J167" s="11"/>
+      <c r="K167" s="11"/>
+      <c r="L167" s="11"/>
+      <c r="M167" s="11"/>
+      <c r="N167" s="11" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A168" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="C168" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="E168" s="12">
+        <v>3876.6</v>
+      </c>
+      <c r="F168" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="G168" s="12">
+        <v>3970</v>
+      </c>
+      <c r="H168" s="12">
+        <v>3951.8</v>
+      </c>
+      <c r="I168" s="12">
+        <v>3959.9</v>
+      </c>
+      <c r="J168" s="11"/>
+      <c r="K168" s="11"/>
+      <c r="L168" s="11"/>
+      <c r="M168" s="11"/>
+      <c r="N168" s="11" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A169" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="E169" s="12">
+        <v>382.5</v>
+      </c>
+      <c r="F169" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="G169" s="12">
+        <v>391.8</v>
+      </c>
+      <c r="H169" s="12">
+        <v>388.9</v>
+      </c>
+      <c r="I169" s="12">
+        <v>391.65</v>
+      </c>
+      <c r="J169" s="11"/>
+      <c r="K169" s="11"/>
+      <c r="L169" s="11"/>
+      <c r="M169" s="11"/>
+      <c r="N169" s="11" t="s">
+        <v>595</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
